--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:52:18+00:00</t>
+    <t>2026-03-27T11:27:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T11:27:16+00:00</t>
+    <t>2026-03-27T16:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T16:10:13+00:00</t>
+    <t>2026-03-27T16:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T16:30:06+00:00</t>
+    <t>2026-03-27T16:32:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T16:32:09+00:00</t>
+    <t>2026-03-30T08:42:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T08:42:52+00:00</t>
+    <t>2026-03-30T08:55:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T08:55:18+00:00</t>
+    <t>2026-03-30T09:31:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T09:31:51+00:00</t>
+    <t>2026-03-30T10:20:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:20:39+00:00</t>
+    <t>2026-03-30T13:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:30:37+00:00</t>
+    <t>2026-03-30T16:30:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T16:30:41+00:00</t>
+    <t>2026-03-31T10:02:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T10:02:00+00:00</t>
+    <t>2026-03-31T16:37:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T16:37:48+00:00</t>
+    <t>2026-03-31T17:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T17:09:58+00:00</t>
+    <t>2026-04-02T08:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T08:54:20+00:00</t>
+    <t>2026-04-02T12:48:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:48:18+00:00</t>
+    <t>2026-04-02T13:07:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:07:09+00:00</t>
+    <t>2026-04-02T14:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T14:06:16+00:00</t>
+    <t>2026-04-08T08:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:33:04+00:00</t>
+    <t>2026-04-14T16:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T16:36:20+00:00</t>
+    <t>2026-04-15T12:53:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:53:13+00:00</t>
+    <t>2026-06-01T14:30:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:30:38+00:00</t>
+    <t>2026-06-01T14:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/add-exemples-iti65/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:30:20+00:00</t>
+    <t>2026-07-29T08:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
